--- a/data/interim/anomaly_test_outputs/va_step2_anomalies.xlsx
+++ b/data/interim/anomaly_test_outputs/va_step2_anomalies.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,45 +439,50 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>uploaded_at</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>usage_kwh</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>demand_kw</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>charges</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Effective_Cost_per_kWh</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Load_Factor</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Eligible_For_Rate_Upgrade</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Is_Usage_Anomaly</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Is_New_Activation</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Anomaly_Reason</t>
         </is>
@@ -497,33 +502,36 @@
       <c r="C2" s="1" t="n">
         <v>45845</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="1" t="n">
+        <v>46081.74531385658</v>
+      </c>
+      <c r="E2" t="n">
         <v>633</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>$85.27</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>$0.13</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
         <v>1</v>
       </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Spike of 2419.8%. Current usage is 20.4 kWh/day vs historical normal of 0.8 kWh/day.</t>
         </is>
@@ -543,33 +551,36 @@
       <c r="C3" s="1" t="n">
         <v>45874</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="1" t="n">
+        <v>46081.74531385658</v>
+      </c>
+      <c r="E3" t="n">
         <v>640</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>$86.39</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>$0.13</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
         <v>1</v>
       </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Spike of 233.7%. Current usage is 22.9 kWh/day vs historical normal of 6.8 kWh/day.</t>
         </is>
@@ -589,33 +600,36 @@
       <c r="C4" s="1" t="n">
         <v>45964</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="1" t="n">
+        <v>46081.74531385658</v>
+      </c>
+      <c r="E4" t="n">
         <v>545</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>$75.11</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>$0.14</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
         <v>1</v>
       </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Spike of 648.0%. Current usage is 18.2 kWh/day vs historical normal of 2.4 kWh/day.</t>
         </is>
